--- a/output/upload/S00026_2259_바로연금보험_무배당.xlsx
+++ b/output/upload/S00026_2259_바로연금보험_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1394,17 +1386,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -1484,17 +1468,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -1574,17 +1550,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -1664,17 +1632,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2259804</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">

--- a/output/upload/S00026_2259_바로연금보험_무배당.xlsx
+++ b/output/upload/S00026_2259_바로연금보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1386,11 +1406,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1468,11 +1508,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1550,11 +1610,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1632,11 +1712,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_2259_바로연금보험_무배당.xlsx
+++ b/output/upload/S00026_2259_바로연금보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1814,31 +1814,83 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>2259851</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)적립</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="J12" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
+      <c r="O12" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n"/>
-      <c r="Y12" s="6" t="n"/>
-      <c r="Z12" s="6" t="n"/>
+      <c r="X12" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y12" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA12" s="6" t="n"/>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
@@ -1864,31 +1916,83 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2259851</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)적립</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA13" s="6" t="n"/>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
@@ -1914,31 +2018,83 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2259851</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)적립</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
+      <c r="O14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA14" s="6" t="n"/>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
@@ -1964,31 +2120,83 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2259851</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)적립</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
+      <c r="O15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
+      <c r="X15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
@@ -2014,31 +2222,83 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2259801</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>2259851</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 개인형)적립</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="J16" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
+      <c r="O16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n"/>
-      <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
+      <c r="X16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA16" s="6" t="n"/>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
@@ -2064,31 +2324,83 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="J17" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
+      <c r="O17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
+      <c r="X17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA17" s="6" t="n"/>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
@@ -2114,31 +2426,83 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="J18" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
+      <c r="O18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
+      <c r="X18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y18" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA18" s="6" t="n"/>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
@@ -2164,31 +2528,83 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
+      <c r="O19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n"/>
-      <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
+      <c r="X19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA19" s="6" t="n"/>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
@@ -2214,31 +2630,83 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="J20" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n"/>
+      <c r="O20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
-      <c r="X20" s="6" t="n"/>
-      <c r="Y20" s="6" t="n"/>
-      <c r="Z20" s="6" t="n"/>
+      <c r="X20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z20" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA20" s="6" t="n"/>
       <c r="AB20" s="6" t="n"/>
       <c r="AC20" s="6" t="n"/>
@@ -2264,31 +2732,83 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
+      <c r="J21" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
+      <c r="O21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
+      <c r="X21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA21" s="6" t="n"/>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
@@ -2314,31 +2834,83 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>2259852</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)적립</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
+      <c r="J22" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
+      <c r="O22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
+      <c r="X22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="AA22" s="6" t="n"/>
       <c r="AB22" s="6" t="n"/>
       <c r="AC22" s="6" t="n"/>
@@ -2362,6 +2934,6586 @@
       <c r="AU22" s="6" t="n"/>
       <c r="AV22" s="6" t="n"/>
     </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2259852</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)적립</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>48</v>
+      </c>
+      <c r="K23" t="n">
+        <v>85</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>999</v>
+      </c>
+      <c r="P23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2259852</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)적립</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K24" t="n">
+        <v>82</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>999</v>
+      </c>
+      <c r="P24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2259852</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)적립</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>45</v>
+      </c>
+      <c r="K25" t="n">
+        <v>80</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>999</v>
+      </c>
+      <c r="P25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2259802</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2259852</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 초기집중형 개인형)적립</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>45</v>
+      </c>
+      <c r="K26" t="n">
+        <v>85</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>999</v>
+      </c>
+      <c r="P26" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>45</v>
+      </c>
+      <c r="K27" t="n">
+        <v>85</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>48</v>
+      </c>
+      <c r="K28" t="n">
+        <v>85</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>999</v>
+      </c>
+      <c r="P28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>82</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>999</v>
+      </c>
+      <c r="P29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>45</v>
+      </c>
+      <c r="K30" t="n">
+        <v>80</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>999</v>
+      </c>
+      <c r="P30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>45</v>
+      </c>
+      <c r="K31" t="n">
+        <v>85</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>999</v>
+      </c>
+      <c r="P31" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2259853</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)적립</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>45</v>
+      </c>
+      <c r="K32" t="n">
+        <v>85</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>999</v>
+      </c>
+      <c r="P32" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2259853</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)적립</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>48</v>
+      </c>
+      <c r="K33" t="n">
+        <v>85</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>999</v>
+      </c>
+      <c r="P33" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2259853</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)적립</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>45</v>
+      </c>
+      <c r="K34" t="n">
+        <v>82</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>999</v>
+      </c>
+      <c r="P34" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2259853</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)적립</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>45</v>
+      </c>
+      <c r="K35" t="n">
+        <v>80</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>999</v>
+      </c>
+      <c r="P35" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2259803</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2259853</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(종신연금형 일반형 신부부형)적립</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>45</v>
+      </c>
+      <c r="K36" t="n">
+        <v>85</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>999</v>
+      </c>
+      <c r="P36" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>45</v>
+      </c>
+      <c r="K37" t="n">
+        <v>85</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>999</v>
+      </c>
+      <c r="P37" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>48</v>
+      </c>
+      <c r="K38" t="n">
+        <v>85</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>999</v>
+      </c>
+      <c r="P38" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>45</v>
+      </c>
+      <c r="K39" t="n">
+        <v>82</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>999</v>
+      </c>
+      <c r="P39" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>45</v>
+      </c>
+      <c r="K40" t="n">
+        <v>80</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>999</v>
+      </c>
+      <c r="P40" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>45</v>
+      </c>
+      <c r="K41" t="n">
+        <v>85</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>999</v>
+      </c>
+      <c r="P41" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2259854</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)적립</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>45</v>
+      </c>
+      <c r="K42" t="n">
+        <v>85</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>999</v>
+      </c>
+      <c r="P42" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2259854</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)적립</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>48</v>
+      </c>
+      <c r="K43" t="n">
+        <v>85</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>999</v>
+      </c>
+      <c r="P43" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2259854</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)적립</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>45</v>
+      </c>
+      <c r="K44" t="n">
+        <v>82</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>999</v>
+      </c>
+      <c r="P44" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2259854</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)적립</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>45</v>
+      </c>
+      <c r="K45" t="n">
+        <v>80</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>999</v>
+      </c>
+      <c r="P45" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2259804</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2259854</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 종신플랜)적립</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>45</v>
+      </c>
+      <c r="K46" t="n">
+        <v>85</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>999</v>
+      </c>
+      <c r="P46" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>45</v>
+      </c>
+      <c r="K47" t="n">
+        <v>85</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>999</v>
+      </c>
+      <c r="P47" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>48</v>
+      </c>
+      <c r="K48" t="n">
+        <v>85</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>999</v>
+      </c>
+      <c r="P48" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>45</v>
+      </c>
+      <c r="K49" t="n">
+        <v>82</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>999</v>
+      </c>
+      <c r="P49" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>45</v>
+      </c>
+      <c r="K50" t="n">
+        <v>80</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>999</v>
+      </c>
+      <c r="P50" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>45</v>
+      </c>
+      <c r="K51" t="n">
+        <v>85</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>999</v>
+      </c>
+      <c r="P51" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2259855</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)적립</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>45</v>
+      </c>
+      <c r="K52" t="n">
+        <v>85</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>999</v>
+      </c>
+      <c r="P52" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2259855</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)적립</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>48</v>
+      </c>
+      <c r="K53" t="n">
+        <v>85</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>999</v>
+      </c>
+      <c r="P53" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2259855</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)적립</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>45</v>
+      </c>
+      <c r="K54" t="n">
+        <v>82</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>999</v>
+      </c>
+      <c r="P54" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2259855</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)적립</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>45</v>
+      </c>
+      <c r="K55" t="n">
+        <v>80</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>999</v>
+      </c>
+      <c r="P55" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2259805</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2259855</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜5년형)적립</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>45</v>
+      </c>
+      <c r="K56" t="n">
+        <v>85</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>999</v>
+      </c>
+      <c r="P56" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>45</v>
+      </c>
+      <c r="K57" t="n">
+        <v>85</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>999</v>
+      </c>
+      <c r="P57" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>48</v>
+      </c>
+      <c r="K58" t="n">
+        <v>85</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>999</v>
+      </c>
+      <c r="P58" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>45</v>
+      </c>
+      <c r="K59" t="n">
+        <v>82</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>999</v>
+      </c>
+      <c r="P59" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>45</v>
+      </c>
+      <c r="K60" t="n">
+        <v>80</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>999</v>
+      </c>
+      <c r="P60" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>45</v>
+      </c>
+      <c r="K61" t="n">
+        <v>85</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>999</v>
+      </c>
+      <c r="P61" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2259856</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)적립</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>45</v>
+      </c>
+      <c r="K62" t="n">
+        <v>85</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>999</v>
+      </c>
+      <c r="P62" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2259856</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)적립</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>48</v>
+      </c>
+      <c r="K63" t="n">
+        <v>85</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>999</v>
+      </c>
+      <c r="P63" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2259856</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)적립</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>45</v>
+      </c>
+      <c r="K64" t="n">
+        <v>82</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>999</v>
+      </c>
+      <c r="P64" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2259856</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)적립</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>45</v>
+      </c>
+      <c r="K65" t="n">
+        <v>80</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>999</v>
+      </c>
+      <c r="P65" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2259806</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2259856</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜10년형)적립</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>45</v>
+      </c>
+      <c r="K66" t="n">
+        <v>85</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>999</v>
+      </c>
+      <c r="P66" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>45</v>
+      </c>
+      <c r="K67" t="n">
+        <v>85</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>999</v>
+      </c>
+      <c r="P67" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>48</v>
+      </c>
+      <c r="K68" t="n">
+        <v>85</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>999</v>
+      </c>
+      <c r="P68" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X68" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>45</v>
+      </c>
+      <c r="K69" t="n">
+        <v>82</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>999</v>
+      </c>
+      <c r="P69" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X69" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>45</v>
+      </c>
+      <c r="K70" t="n">
+        <v>80</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>999</v>
+      </c>
+      <c r="P70" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X70" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>45</v>
+      </c>
+      <c r="K71" t="n">
+        <v>85</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>999</v>
+      </c>
+      <c r="P71" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2259857</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)적립</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>45</v>
+      </c>
+      <c r="K72" t="n">
+        <v>85</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>999</v>
+      </c>
+      <c r="P72" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X72" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2259857</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)적립</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>48</v>
+      </c>
+      <c r="K73" t="n">
+        <v>85</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>999</v>
+      </c>
+      <c r="P73" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X73" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2259857</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)적립</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>45</v>
+      </c>
+      <c r="K74" t="n">
+        <v>82</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>999</v>
+      </c>
+      <c r="P74" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X74" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2259857</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)적립</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>45</v>
+      </c>
+      <c r="K75" t="n">
+        <v>80</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>999</v>
+      </c>
+      <c r="P75" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X75" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2259807</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2259857</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(상속연금형 환급플랜20년형)적립</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>45</v>
+      </c>
+      <c r="K76" t="n">
+        <v>85</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>999</v>
+      </c>
+      <c r="P76" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>45</v>
+      </c>
+      <c r="K77" t="n">
+        <v>85</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>999</v>
+      </c>
+      <c r="P77" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X77" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>48</v>
+      </c>
+      <c r="K78" t="n">
+        <v>85</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>999</v>
+      </c>
+      <c r="P78" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X78" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>45</v>
+      </c>
+      <c r="K79" t="n">
+        <v>82</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>999</v>
+      </c>
+      <c r="P79" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X79" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>45</v>
+      </c>
+      <c r="K80" t="n">
+        <v>80</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>999</v>
+      </c>
+      <c r="P80" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X80" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>45</v>
+      </c>
+      <c r="K81" t="n">
+        <v>85</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>999</v>
+      </c>
+      <c r="P81" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2259858</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)적립</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>45</v>
+      </c>
+      <c r="K82" t="n">
+        <v>85</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>999</v>
+      </c>
+      <c r="P82" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X82" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2259858</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)적립</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>48</v>
+      </c>
+      <c r="K83" t="n">
+        <v>85</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>999</v>
+      </c>
+      <c r="P83" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X83" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2259858</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)적립</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>45</v>
+      </c>
+      <c r="K84" t="n">
+        <v>82</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>999</v>
+      </c>
+      <c r="P84" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X84" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2259858</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)적립</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>45</v>
+      </c>
+      <c r="K85" t="n">
+        <v>80</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>999</v>
+      </c>
+      <c r="P85" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X85" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2259808</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2259858</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 5년형)적립</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>45</v>
+      </c>
+      <c r="K86" t="n">
+        <v>85</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>999</v>
+      </c>
+      <c r="P86" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>45</v>
+      </c>
+      <c r="K87" t="n">
+        <v>85</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>999</v>
+      </c>
+      <c r="P87" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X87" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>48</v>
+      </c>
+      <c r="K88" t="n">
+        <v>85</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>999</v>
+      </c>
+      <c r="P88" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X88" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>45</v>
+      </c>
+      <c r="K89" t="n">
+        <v>82</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>999</v>
+      </c>
+      <c r="P89" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X89" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>45</v>
+      </c>
+      <c r="K90" t="n">
+        <v>80</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>999</v>
+      </c>
+      <c r="P90" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X90" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>45</v>
+      </c>
+      <c r="K91" t="n">
+        <v>85</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>999</v>
+      </c>
+      <c r="P91" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2259859</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)적립</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>45</v>
+      </c>
+      <c r="K92" t="n">
+        <v>85</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>999</v>
+      </c>
+      <c r="P92" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X92" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2259859</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)적립</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>48</v>
+      </c>
+      <c r="K93" t="n">
+        <v>85</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>999</v>
+      </c>
+      <c r="P93" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X93" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2259859</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)적립</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>45</v>
+      </c>
+      <c r="K94" t="n">
+        <v>82</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>999</v>
+      </c>
+      <c r="P94" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X94" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2259859</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)적립</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>45</v>
+      </c>
+      <c r="K95" t="n">
+        <v>80</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>999</v>
+      </c>
+      <c r="P95" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X95" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2259809</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2259859</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 10년형)적립</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>45</v>
+      </c>
+      <c r="K96" t="n">
+        <v>85</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>999</v>
+      </c>
+      <c r="P96" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>45</v>
+      </c>
+      <c r="K97" t="n">
+        <v>85</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>999</v>
+      </c>
+      <c r="P97" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X97" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>48</v>
+      </c>
+      <c r="K98" t="n">
+        <v>85</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>999</v>
+      </c>
+      <c r="P98" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X98" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>45</v>
+      </c>
+      <c r="K99" t="n">
+        <v>82</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>999</v>
+      </c>
+      <c r="P99" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X99" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>45</v>
+      </c>
+      <c r="K100" t="n">
+        <v>80</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>999</v>
+      </c>
+      <c r="P100" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X100" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>45</v>
+      </c>
+      <c r="K101" t="n">
+        <v>85</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>999</v>
+      </c>
+      <c r="P101" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2259860</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)적립</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>45</v>
+      </c>
+      <c r="K102" t="n">
+        <v>85</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>999</v>
+      </c>
+      <c r="P102" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X102" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2259860</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)적립</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>48</v>
+      </c>
+      <c r="K103" t="n">
+        <v>85</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>999</v>
+      </c>
+      <c r="P103" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X103" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2259860</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)적립</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>45</v>
+      </c>
+      <c r="K104" t="n">
+        <v>82</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
+        <v>999</v>
+      </c>
+      <c r="P104" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X104" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2259860</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)적립</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>45</v>
+      </c>
+      <c r="K105" t="n">
+        <v>80</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
+        <v>999</v>
+      </c>
+      <c r="P105" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X105" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2259810</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2259860</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 15년형)적립</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>45</v>
+      </c>
+      <c r="K106" t="n">
+        <v>85</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
+        <v>999</v>
+      </c>
+      <c r="P106" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>45</v>
+      </c>
+      <c r="K107" t="n">
+        <v>85</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
+        <v>999</v>
+      </c>
+      <c r="P107" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X107" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>48</v>
+      </c>
+      <c r="K108" t="n">
+        <v>85</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
+        <v>999</v>
+      </c>
+      <c r="P108" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X108" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>45</v>
+      </c>
+      <c r="K109" t="n">
+        <v>82</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
+        <v>999</v>
+      </c>
+      <c r="P109" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X109" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>45</v>
+      </c>
+      <c r="K110" t="n">
+        <v>80</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
+        <v>999</v>
+      </c>
+      <c r="P110" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X110" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>45</v>
+      </c>
+      <c r="K111" t="n">
+        <v>85</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O111" t="n">
+        <v>999</v>
+      </c>
+      <c r="P111" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2259861</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)적립</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>45</v>
+      </c>
+      <c r="K112" t="n">
+        <v>85</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
+        <v>999</v>
+      </c>
+      <c r="P112" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X112" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2259861</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)적립</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>48</v>
+      </c>
+      <c r="K113" t="n">
+        <v>85</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
+        <v>999</v>
+      </c>
+      <c r="P113" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X113" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2259861</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)적립</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>45</v>
+      </c>
+      <c r="K114" t="n">
+        <v>82</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>999</v>
+      </c>
+      <c r="P114" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X114" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2259861</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)적립</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>45</v>
+      </c>
+      <c r="K115" t="n">
+        <v>80</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
+        <v>999</v>
+      </c>
+      <c r="P115" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X115" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2259811</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2259861</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>한화생명 바로연금보험 무배당(확정기간연금형 20년형)적립</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>45</v>
+      </c>
+      <c r="K116" t="n">
+        <v>85</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="O116" t="n">
+        <v>999</v>
+      </c>
+      <c r="P116" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="L3:AV3"/>
